--- a/Altium/SNAPCBVersion-INT/BOM/SNAPCBVersion_SNA-Var_EMS_BOM_Rev.PCBVersion1.0.xlsx
+++ b/Altium/SNAPCBVersion-INT/BOM/SNAPCBVersion_SNA-Var_EMS_BOM_Rev.PCBVersion1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C4DCD3C-03A2-4BBF-86A4-7D65F9AAD78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DB6909-50EC-4977-AEAD-C15EEE7D608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27540" yWindow="2145" windowWidth="21600" windowHeight="11295" xr2:uid="{77D22291-FFF1-4BF4-9D9E-F1A56B230E06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{77D22291-FFF1-4BF4-9D9E-F1A56B230E06}"/>
   </bookViews>
   <sheets>
     <sheet name="SNAPCBVersion_SNA-Var_EMS_BOM_R" sheetId="1" r:id="rId1"/>
@@ -1652,15 +1652,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1676,7 +1685,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1993,9 +2002,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05F3CF7D-12E5-448D-9CBE-DC818BADCCA9}">
   <dimension ref="A1:M77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="56.28515625" customWidth="1"/>
+    <col min="3" max="3" width="73.42578125" style="7" customWidth="1"/>
+    <col min="4" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="35.5703125" customWidth="1"/>
+    <col min="9" max="10" width="16.5703125" customWidth="1"/>
     <col min="11" max="11" width="27.42578125" customWidth="1"/>
     <col min="12" max="12" width="11.140625" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
@@ -2008,7 +2022,7 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -2049,7 +2063,7 @@
       <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -2088,7 +2102,7 @@
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -2118,14 +2132,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -2164,7 +2178,7 @@
       <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -2201,7 +2215,7 @@
       <c r="B6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -2233,14 +2247,14 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -2270,14 +2284,14 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -2316,7 +2330,7 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -2355,7 +2369,7 @@
       <c r="B10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>72</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -2392,7 +2406,7 @@
       <c r="B11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -2422,14 +2436,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>83</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -2468,7 +2482,7 @@
       <c r="B13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -2507,7 +2521,7 @@
       <c r="B14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="6" t="s">
         <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -2546,7 +2560,7 @@
       <c r="B15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="6" t="s">
         <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -2585,7 +2599,7 @@
       <c r="B16" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="6" t="s">
         <v>107</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -2622,7 +2636,7 @@
       <c r="B17" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -2659,7 +2673,7 @@
       <c r="B18" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="6" t="s">
         <v>122</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -2692,7 +2706,7 @@
       <c r="B19" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>128</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -2729,7 +2743,7 @@
       <c r="B20" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>134</v>
       </c>
       <c r="D20" s="2" t="s">
@@ -2768,7 +2782,7 @@
       <c r="B21" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -2807,7 +2821,7 @@
       <c r="B22" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="6" t="s">
         <v>150</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -2844,7 +2858,7 @@
       <c r="B23" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="6" t="s">
         <v>156</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -2883,7 +2897,7 @@
       <c r="B24" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>161</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -2922,7 +2936,7 @@
       <c r="B25" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="6" t="s">
         <v>168</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -2961,7 +2975,7 @@
       <c r="B26" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="6" t="s">
         <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -3000,7 +3014,7 @@
       <c r="B27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -3037,7 +3051,7 @@
       <c r="B28" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="6" t="s">
         <v>191</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -3076,7 +3090,7 @@
       <c r="B29" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="6" t="s">
         <v>199</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -3115,7 +3129,7 @@
       <c r="B30" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="6" t="s">
         <v>207</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -3147,14 +3161,14 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="6" t="s">
         <v>214</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -3191,7 +3205,7 @@
       <c r="B32" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="6" t="s">
         <v>221</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -3230,7 +3244,7 @@
       <c r="B33" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="6" t="s">
         <v>229</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -3267,7 +3281,7 @@
       <c r="B34" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="6" t="s">
         <v>236</v>
       </c>
       <c r="D34" s="2" t="s">
@@ -3306,7 +3320,7 @@
       <c r="B35" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="6" t="s">
         <v>244</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -3345,7 +3359,7 @@
       <c r="B36" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="6" t="s">
         <v>252</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -3384,7 +3398,7 @@
       <c r="B37" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="6" t="s">
         <v>258</v>
       </c>
       <c r="D37" s="2" t="s">
@@ -3423,7 +3437,7 @@
       <c r="B38" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="6" t="s">
         <v>264</v>
       </c>
       <c r="D38" s="2" t="s">
@@ -3462,7 +3476,7 @@
       <c r="B39" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="6" t="s">
         <v>271</v>
       </c>
       <c r="D39" s="2" t="s">
@@ -3499,7 +3513,7 @@
       <c r="B40" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="6" t="s">
         <v>277</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -3536,7 +3550,7 @@
       <c r="B41" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D41" s="2" t="s">
@@ -3573,7 +3587,7 @@
       <c r="B42" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="6" t="s">
         <v>289</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -3603,14 +3617,14 @@
         <v>287</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>262</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="6" t="s">
         <v>296</v>
       </c>
       <c r="D43" s="2" t="s">
@@ -3649,7 +3663,7 @@
       <c r="B44" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="6" t="s">
         <v>302</v>
       </c>
       <c r="D44" s="2" t="s">
@@ -3686,7 +3700,7 @@
       <c r="B45" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="6" t="s">
         <v>306</v>
       </c>
       <c r="D45" s="2" t="s">
@@ -3725,7 +3739,7 @@
       <c r="B46" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="6" t="s">
         <v>312</v>
       </c>
       <c r="D46" s="2" t="s">
@@ -3757,14 +3771,14 @@
         <v>310</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="6" t="s">
         <v>318</v>
       </c>
       <c r="D47" s="2" t="s">
@@ -3803,7 +3817,7 @@
       <c r="B48" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="6" t="s">
         <v>324</v>
       </c>
       <c r="D48" s="2" t="s">
@@ -3836,7 +3850,7 @@
       <c r="B49" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>328</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -3873,7 +3887,7 @@
       <c r="B50" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="6" t="s">
         <v>334</v>
       </c>
       <c r="D50" s="2" t="s">
@@ -3910,7 +3924,7 @@
       <c r="B51" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="6" t="s">
         <v>340</v>
       </c>
       <c r="D51" s="2" t="s">
@@ -3949,7 +3963,7 @@
       <c r="B52" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="6" t="s">
         <v>347</v>
       </c>
       <c r="D52" s="2" t="s">
@@ -3988,7 +4002,7 @@
       <c r="B53" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="6" t="s">
         <v>353</v>
       </c>
       <c r="D53" s="2" t="s">
@@ -4027,7 +4041,7 @@
       <c r="B54" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="6" t="s">
         <v>359</v>
       </c>
       <c r="D54" s="2" t="s">
@@ -4060,7 +4074,7 @@
       <c r="B55" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="6" t="s">
         <v>364</v>
       </c>
       <c r="D55" s="2" t="s">
@@ -4099,7 +4113,7 @@
       <c r="B56" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="6" t="s">
         <v>371</v>
       </c>
       <c r="D56" s="2" t="s">
@@ -4138,7 +4152,7 @@
       <c r="B57" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="6" t="s">
         <v>377</v>
       </c>
       <c r="D57" s="2" t="s">
@@ -4177,7 +4191,7 @@
       <c r="B58" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="6" t="s">
         <v>383</v>
       </c>
       <c r="D58" s="2" t="s">
@@ -4216,7 +4230,7 @@
       <c r="B59" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="6" t="s">
         <v>390</v>
       </c>
       <c r="D59" s="2" t="s">
@@ -4255,7 +4269,7 @@
       <c r="B60" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="6" t="s">
         <v>396</v>
       </c>
       <c r="D60" s="2" t="s">
@@ -4294,7 +4308,7 @@
       <c r="B61" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="6" t="s">
         <v>404</v>
       </c>
       <c r="D61" s="2" t="s">
@@ -4331,7 +4345,7 @@
       <c r="B62" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="6" t="s">
         <v>411</v>
       </c>
       <c r="D62" s="2" t="s">
@@ -4370,7 +4384,7 @@
       <c r="B63" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="6" t="s">
         <v>419</v>
       </c>
       <c r="D63" s="2" t="s">
@@ -4407,7 +4421,7 @@
       <c r="B64" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="6" t="s">
         <v>427</v>
       </c>
       <c r="D64" s="2" t="s">
@@ -4444,7 +4458,7 @@
       <c r="B65" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="6" t="s">
         <v>434</v>
       </c>
       <c r="D65" s="2" t="s">
@@ -4481,7 +4495,7 @@
       <c r="B66" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="6" t="s">
         <v>440</v>
       </c>
       <c r="D66" s="2" t="s">
@@ -4520,7 +4534,7 @@
       <c r="B67" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="6" t="s">
         <v>446</v>
       </c>
       <c r="D67" s="2" t="s">
@@ -4557,7 +4571,7 @@
       <c r="B68" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="6" t="s">
         <v>453</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -4596,7 +4610,7 @@
       <c r="B69" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="6" t="s">
         <v>460</v>
       </c>
       <c r="D69" s="2" t="s">
@@ -4635,7 +4649,7 @@
       <c r="B70" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="6" t="s">
         <v>467</v>
       </c>
       <c r="D70" s="2" t="s">
@@ -4674,7 +4688,7 @@
       <c r="B71" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="6" t="s">
         <v>475</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -4713,7 +4727,7 @@
       <c r="B72" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="6" t="s">
         <v>482</v>
       </c>
       <c r="D72" s="2" t="s">
@@ -4752,7 +4766,7 @@
       <c r="B73" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="6" t="s">
         <v>489</v>
       </c>
       <c r="D73" s="2" t="s">
@@ -4791,7 +4805,7 @@
       <c r="B74" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="6" t="s">
         <v>496</v>
       </c>
       <c r="D74" s="2" t="s">
@@ -4830,7 +4844,7 @@
       <c r="B75" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="6" t="s">
         <v>502</v>
       </c>
       <c r="D75" s="2" t="s">
@@ -4869,7 +4883,7 @@
       <c r="B76" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="6" t="s">
         <v>508</v>
       </c>
       <c r="D76" s="2" t="s">
@@ -4908,7 +4922,7 @@
       <c r="B77" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="6" t="s">
         <v>514</v>
       </c>
       <c r="D77" s="2" t="s">

--- a/Altium/SNAPCBVersion-INT/BOM/SNAPCBVersion_SNA-Var_EMS_BOM_Rev.PCBVersion1.0.xlsx
+++ b/Altium/SNAPCBVersion-INT/BOM/SNAPCBVersion_SNA-Var_EMS_BOM_Rev.PCBVersion1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ml\repos\BK\SNA\Altium\SNAPCBVersion-INT\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maell\repos\private\SNA\Altium\SNAPCBVersion-INT\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C4DCD3C-03A2-4BBF-86A4-7D65F9AAD78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DB6909-50EC-4977-AEAD-C15EEE7D608A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27540" yWindow="2145" windowWidth="21600" windowHeight="11295" xr2:uid="{77D22291-FFF1-4BF4-9D9E-F1A56B230E06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{77D22291-FFF1-4BF4-9D9E-F1A56B230E06}"/>
   </bookViews>
   <sheets>
     <sheet name="SNAPCBVersion_SNA-Var_EMS_BOM_R" sheetId="1" r:id="rId1"/>
@@ -1652,15 +1652,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1676,7 +1685,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1993,9 +2002,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05F3CF7D-12E5-448D-9CBE-DC818BADCCA9}">
   <dimension ref="A1:M77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="56.28515625" customWidth="1"/>
+    <col min="3" max="3" width="73.42578125" style="7" customWidth="1"/>
+    <col min="4" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="35.5703125" customWidth="1"/>
+    <col min="9" max="10" width="16.5703125" customWidth="1"/>
     <col min="11" max="11" width="27.42578125" customWidth="1"/>
     <col min="12" max="12" width="11.140625" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
@@ -2008,7 +2022,7 @@
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -2049,7 +2063,7 @@
       <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -2088,7 +2102,7 @@
       <c r="B3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -2118,14 +2132,14 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -2164,7 +2178,7 @@
       <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -2201,7 +2215,7 @@
       <c r="B6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -2233,14 +2247,14 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -2270,14 +2284,14 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -2316,7 +2330,7 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -2355,7 +2369,7 @@
       <c r="B10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>72</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -2392,7 +2406,7 @@
       <c r="B11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -2422,14 +2436,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>83</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -2468,7 +2482,7 @@
       <c r="B13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -2507,7 +2521,7 @@
       <c r="B14" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="6" t="s">
         <v>95</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -2546,7 +2560,7 @@
       <c r="B15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="6" t="s">
         <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -2585,7 +2599,7 @@
       <c r="B16" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="6" t="s">
         <v>107</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -2622,7 +2636,7 @@
       <c r="B17" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -2659,7 +2673,7 @@
       <c r="B18" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="6" t="s">
         <v>122</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -2692,7 +2706,7 @@
       <c r="B19" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>128</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -2729,7 +2743,7 @@
       <c r="B20" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>134</v>
       </c>
       <c r="D20" s="2" t="s">
@@ -2768,7 +2782,7 @@
       <c r="B21" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="6" t="s">
         <v>143</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -2807,7 +2821,7 @@
       <c r="B22" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="6" t="s">
         <v>150</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -2844,7 +2858,7 @@
       <c r="B23" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="6" t="s">
         <v>156</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -2883,7 +2897,7 @@
       <c r="B24" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>161</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -2922,7 +2936,7 @@
       <c r="B25" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="6" t="s">
         <v>168</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -2961,7 +2975,7 @@
       <c r="B26" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="6" t="s">
         <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -3000,7 +3014,7 @@
       <c r="B27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -3037,7 +3051,7 @@
       <c r="B28" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="6" t="s">
         <v>191</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -3076,7 +3090,7 @@
       <c r="B29" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="6" t="s">
         <v>199</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -3115,7 +3129,7 @@
       <c r="B30" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="6" t="s">
         <v>207</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -3147,14 +3161,14 @@
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="6" t="s">
         <v>214</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -3191,7 +3205,7 @@
       <c r="B32" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="6" t="s">
         <v>221</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -3230,7 +3244,7 @@
       <c r="B33" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="6" t="s">
         <v>229</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -3267,7 +3281,7 @@
       <c r="B34" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="6" t="s">
         <v>236</v>
       </c>
       <c r="D34" s="2" t="s">
@@ -3306,7 +3320,7 @@
       <c r="B35" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="6" t="s">
         <v>244</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -3345,7 +3359,7 @@
       <c r="B36" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="6" t="s">
         <v>252</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -3384,7 +3398,7 @@
       <c r="B37" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="6" t="s">
         <v>258</v>
       </c>
       <c r="D37" s="2" t="s">
@@ -3423,7 +3437,7 @@
       <c r="B38" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="6" t="s">
         <v>264</v>
       </c>
       <c r="D38" s="2" t="s">
@@ -3462,7 +3476,7 @@
       <c r="B39" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="6" t="s">
         <v>271</v>
       </c>
       <c r="D39" s="2" t="s">
@@ -3499,7 +3513,7 @@
       <c r="B40" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="6" t="s">
         <v>277</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -3536,7 +3550,7 @@
       <c r="B41" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="6" t="s">
         <v>283</v>
       </c>
       <c r="D41" s="2" t="s">
@@ -3573,7 +3587,7 @@
       <c r="B42" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="6" t="s">
         <v>289</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -3603,14 +3617,14 @@
         <v>287</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>262</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="6" t="s">
         <v>296</v>
       </c>
       <c r="D43" s="2" t="s">
@@ -3649,7 +3663,7 @@
       <c r="B44" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="6" t="s">
         <v>302</v>
       </c>
       <c r="D44" s="2" t="s">
@@ -3686,7 +3700,7 @@
       <c r="B45" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="6" t="s">
         <v>306</v>
       </c>
       <c r="D45" s="2" t="s">
@@ -3725,7 +3739,7 @@
       <c r="B46" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="6" t="s">
         <v>312</v>
       </c>
       <c r="D46" s="2" t="s">
@@ -3757,14 +3771,14 @@
         <v>310</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="6" t="s">
         <v>318</v>
       </c>
       <c r="D47" s="2" t="s">
@@ -3803,7 +3817,7 @@
       <c r="B48" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="6" t="s">
         <v>324</v>
       </c>
       <c r="D48" s="2" t="s">
@@ -3836,7 +3850,7 @@
       <c r="B49" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>328</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -3873,7 +3887,7 @@
       <c r="B50" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="6" t="s">
         <v>334</v>
       </c>
       <c r="D50" s="2" t="s">
@@ -3910,7 +3924,7 @@
       <c r="B51" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="6" t="s">
         <v>340</v>
       </c>
       <c r="D51" s="2" t="s">
@@ -3949,7 +3963,7 @@
       <c r="B52" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="6" t="s">
         <v>347</v>
       </c>
       <c r="D52" s="2" t="s">
@@ -3988,7 +4002,7 @@
       <c r="B53" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="6" t="s">
         <v>353</v>
       </c>
       <c r="D53" s="2" t="s">
@@ -4027,7 +4041,7 @@
       <c r="B54" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="6" t="s">
         <v>359</v>
       </c>
       <c r="D54" s="2" t="s">
@@ -4060,7 +4074,7 @@
       <c r="B55" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="6" t="s">
         <v>364</v>
       </c>
       <c r="D55" s="2" t="s">
@@ -4099,7 +4113,7 @@
       <c r="B56" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="6" t="s">
         <v>371</v>
       </c>
       <c r="D56" s="2" t="s">
@@ -4138,7 +4152,7 @@
       <c r="B57" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="6" t="s">
         <v>377</v>
       </c>
       <c r="D57" s="2" t="s">
@@ -4177,7 +4191,7 @@
       <c r="B58" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="6" t="s">
         <v>383</v>
       </c>
       <c r="D58" s="2" t="s">
@@ -4216,7 +4230,7 @@
       <c r="B59" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="6" t="s">
         <v>390</v>
       </c>
       <c r="D59" s="2" t="s">
@@ -4255,7 +4269,7 @@
       <c r="B60" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="6" t="s">
         <v>396</v>
       </c>
       <c r="D60" s="2" t="s">
@@ -4294,7 +4308,7 @@
       <c r="B61" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="6" t="s">
         <v>404</v>
       </c>
       <c r="D61" s="2" t="s">
@@ -4331,7 +4345,7 @@
       <c r="B62" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="6" t="s">
         <v>411</v>
       </c>
       <c r="D62" s="2" t="s">
@@ -4370,7 +4384,7 @@
       <c r="B63" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="6" t="s">
         <v>419</v>
       </c>
       <c r="D63" s="2" t="s">
@@ -4407,7 +4421,7 @@
       <c r="B64" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="6" t="s">
         <v>427</v>
       </c>
       <c r="D64" s="2" t="s">
@@ -4444,7 +4458,7 @@
       <c r="B65" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="6" t="s">
         <v>434</v>
       </c>
       <c r="D65" s="2" t="s">
@@ -4481,7 +4495,7 @@
       <c r="B66" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="6" t="s">
         <v>440</v>
       </c>
       <c r="D66" s="2" t="s">
@@ -4520,7 +4534,7 @@
       <c r="B67" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="6" t="s">
         <v>446</v>
       </c>
       <c r="D67" s="2" t="s">
@@ -4557,7 +4571,7 @@
       <c r="B68" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="6" t="s">
         <v>453</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -4596,7 +4610,7 @@
       <c r="B69" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="6" t="s">
         <v>460</v>
       </c>
       <c r="D69" s="2" t="s">
@@ -4635,7 +4649,7 @@
       <c r="B70" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="6" t="s">
         <v>467</v>
       </c>
       <c r="D70" s="2" t="s">
@@ -4674,7 +4688,7 @@
       <c r="B71" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="6" t="s">
         <v>475</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -4713,7 +4727,7 @@
       <c r="B72" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="6" t="s">
         <v>482</v>
       </c>
       <c r="D72" s="2" t="s">
@@ -4752,7 +4766,7 @@
       <c r="B73" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="6" t="s">
         <v>489</v>
       </c>
       <c r="D73" s="2" t="s">
@@ -4791,7 +4805,7 @@
       <c r="B74" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="6" t="s">
         <v>496</v>
       </c>
       <c r="D74" s="2" t="s">
@@ -4830,7 +4844,7 @@
       <c r="B75" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="6" t="s">
         <v>502</v>
       </c>
       <c r="D75" s="2" t="s">
@@ -4869,7 +4883,7 @@
       <c r="B76" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="6" t="s">
         <v>508</v>
       </c>
       <c r="D76" s="2" t="s">
@@ -4908,7 +4922,7 @@
       <c r="B77" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C77" s="6" t="s">
         <v>514</v>
       </c>
       <c r="D77" s="2" t="s">
